--- a/data/core_conferences_normalized_tags.xlsx
+++ b/data/core_conferences_normalized_tags.xlsx
@@ -963,7 +963,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>https://miccai.org/upcoming-conferences/</x:v>
+        <x:v>https://conferences.miccai.org/2027/en/default.asp</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/1607/</x:v>
@@ -1157,7 +1157,7 @@
         <x:v>Paper-based / workshop-style conference</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>https://signalprocessingsociety.org/tags/mlsp-2027</x:v>
+        <x:v>https://2027.ieeemlsp.org/</x:v>
       </x:c>
       <x:c r="H23"/>
       <x:c r="I23"/>
@@ -1325,7 +1325,7 @@
         <x:v>Paper-based / engineering-focused</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>https://ieee-ner.org/</x:v>
+        <x:v>https://neuro.embs.org/2027/</x:v>
       </x:c>
       <x:c r="H29"/>
       <x:c r="I29"/>
@@ -1905,7 +1905,7 @@
         <x:v>Paper-based / interdisciplinary</x:v>
       </x:c>
       <x:c r="G45" t="str">
-        <x:v>https://www.ida-society.org/</x:v>
+        <x:v>https://ida2027.eu/</x:v>
       </x:c>
       <x:c r="H45" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/845/</x:v>
@@ -2125,7 +2125,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G51" t="str">
-        <x:v>https://icpr2026.org/</x:v>
+        <x:v>https://icpr2028.org/</x:v>
       </x:c>
       <x:c r="H51" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/1169/</x:v>
@@ -2167,7 +2167,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G52" t="str">
-        <x:v>https://iapr.org/</x:v>
+        <x:v>http://acpr2027.com/</x:v>
       </x:c>
       <x:c r="H52"/>
       <x:c r="I52"/>
@@ -2263,7 +2263,7 @@
         <x:v>Paper-based / symposium series</x:v>
       </x:c>
       <x:c r="G55" t="str">
-        <x:v>https://ssci2027generalchairs.github.io/ssci-2027/</x:v>
+        <x:v>https://attend.ieee.org/ssci-2027/</x:v>
       </x:c>
       <x:c r="H55"/>
       <x:c r="I55"/>
@@ -2323,7 +2323,7 @@
         <x:v>Paper-based / Springer proceedings</x:v>
       </x:c>
       <x:c r="G57" t="str">
-        <x:v>https://ais2026.icas.events/</x:v>
+        <x:v>https://ais2027.icas.events/</x:v>
       </x:c>
       <x:c r="H57"/>
       <x:c r="I57"/>
@@ -2739,7 +2739,7 @@
         <x:v>Abstract-based</x:v>
       </x:c>
       <x:c r="G71" t="str">
-        <x:v>https://cssociety.org/ccs/</x:v>
+        <x:v>https://ccs27.pwr.edu.pl/</x:v>
       </x:c>
       <x:c r="H71"/>
       <x:c r="I71"/>
@@ -3197,7 +3197,7 @@
         <x:v>Paper-based / formal and symbolic AI</x:v>
       </x:c>
       <x:c r="G85" t="str">
-        <x:v>https://kr.org/</x:v>
+        <x:v>https://kr.org/KR2027/</x:v>
       </x:c>
       <x:c r="H85" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/1239/</x:v>
@@ -4388,7 +4388,7 @@
       </x:c>
       <x:c r="E118"/>
       <x:c r="F118" s="12" t="str">
-        <x:v>Abstract-based + selected journal papers</x:v>
+        <x:v>Abstract-based + optional full-length papers</x:v>
       </x:c>
       <x:c r="G118" t="str">
         <x:v>https://nodycon2026.app.earendelplatform.com/</x:v>
@@ -4559,7 +4559,7 @@
         <x:v>Abstract-based</x:v>
       </x:c>
       <x:c r="G124" t="str">
-        <x:v>https://areadne.org/</x:v>
+        <x:v>https://areadne.org/2028/home.html</x:v>
       </x:c>
       <x:c r="H124"/>
       <x:c r="I124"/>

--- a/data/core_conferences_normalized_tags.xlsx
+++ b/data/core_conferences_normalized_tags.xlsx
@@ -393,7 +393,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>https://neurips.cc/Conferences/2026</x:v>
+        <x:v>https://neurips.cc/</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/98/</x:v>
@@ -481,7 +481,7 @@
         <x:v>Paper-based / OpenReview</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>https://iclr.cc/Conferences/2027</x:v>
+        <x:v>https://iclr.cc/</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/2273/</x:v>
@@ -525,7 +525,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G5" t="str">
-        <x:v>https://aistats.org/aistats2027/index.html</x:v>
+        <x:v>https://aistats.org/</x:v>
       </x:c>
       <x:c r="H5" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/913/</x:v>
@@ -735,7 +735,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>https://icdm2026.neu.edu.cn/</x:v>
+        <x:v>https://icdm.zhonghuapu.com/main.shtml</x:v>
       </x:c>
       <x:c r="H10" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/642/</x:v>
@@ -771,7 +771,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>https://www.siam.org/conferences-events/siam-conferences/sdm26/</x:v>
+        <x:v>https://www.siam.org/get-involved/connect-with-a-community/activity-groups/data-science/</x:v>
       </x:c>
       <x:c r="H11" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/1727/</x:v>
@@ -815,7 +815,7 @@
         <x:v>Paper-based / applied tracks</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>https://dsaa-2026.vercel.app/</x:v>
+        <x:v>https://dsaa.co/</x:v>
       </x:c>
       <x:c r="H12" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/2237/</x:v>
@@ -1439,7 +1439,7 @@
         <x:v>Paper-based / interdisciplinary</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>https://www.aies-conference.com/2026/</x:v>
+        <x:v>https://www.aies-conference.com/</x:v>
       </x:c>
       <x:c r="H33" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/2354/</x:v>
@@ -1523,7 +1523,7 @@
         <x:v>Paper-based / OpenReview</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>https://aaai.org/conference/aaai/aaai-27/</x:v>
+        <x:v>https://aaai.org/conference/aaai/</x:v>
       </x:c>
       <x:c r="H35" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/1629/</x:v>
@@ -1675,7 +1675,7 @@
         <x:v>Paper-based / OpenReview</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>https://www.acml-conf.org/2026/</x:v>
+        <x:v>https://www.acml-conf.org/</x:v>
       </x:c>
       <x:c r="H39" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/2174/</x:v>
@@ -1755,7 +1755,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>https://cikm2026.diag.uniroma1.it/</x:v>
+        <x:v>http://www.cikmconference.org/</x:v>
       </x:c>
       <x:c r="H41" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/25/</x:v>
@@ -1841,7 +1841,7 @@
         <x:v>Paper-based / mixed tracks</x:v>
       </x:c>
       <x:c r="G43" t="str">
-        <x:v>https://bigdataieee.org/BigData2026/</x:v>
+        <x:v>https://bigdataieee.org/</x:v>
       </x:c>
       <x:c r="H43" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/2274/</x:v>
@@ -1949,7 +1949,7 @@
         <x:v>Paper-based / special sessions</x:v>
       </x:c>
       <x:c r="G46" t="str">
-        <x:v>https://adma2026.github.io/</x:v>
+        <x:v>https://adma2027.github.io/</x:v>
       </x:c>
       <x:c r="H46" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/888/</x:v>
@@ -2233,7 +2233,7 @@
         <x:v>Paper-based / special sessions</x:v>
       </x:c>
       <x:c r="G54" t="str">
-        <x:v>https://www.icmla-conference.org/icmla26/</x:v>
+        <x:v>https://www.icmla-conference.org/icmla27/</x:v>
       </x:c>
       <x:c r="H54" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/1122/</x:v>
@@ -2415,7 +2415,7 @@
         <x:v>Workshop / paper-based</x:v>
       </x:c>
       <x:c r="G60" t="str">
-        <x:v>https://ecml-aaltd.github.io/aaltd2026/</x:v>
+        <x:v>https://ecmlpkdd.org/</x:v>
       </x:c>
       <x:c r="H60"/>
       <x:c r="I60"/>
@@ -2627,7 +2627,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G67" t="str">
-        <x:v>https://acc2027.a2c2.org/</x:v>
+        <x:v>https://acc2028.a2c2.org/</x:v>
       </x:c>
       <x:c r="H67"/>
       <x:c r="I67"/>
@@ -2683,7 +2683,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G69" t="str">
-        <x:v>https://nolta2026.org/</x:v>
+        <x:v>https://www.ieice.org/nolta/conferences/symposium/</x:v>
       </x:c>
       <x:c r="H69"/>
       <x:c r="I69"/>
@@ -3275,7 +3275,7 @@
         <x:v>Paper-based / OpenReview</x:v>
       </x:c>
       <x:c r="G87" t="str">
-        <x:v>https://3dvconf.github.io/2027/</x:v>
+        <x:v>https://3dvconf.github.io/</x:v>
       </x:c>
       <x:c r="H87"/>
       <x:c r="I87" t="str">
@@ -3381,7 +3381,7 @@
         <x:v>Paper-based / BMVA proceedings</x:v>
       </x:c>
       <x:c r="G90" t="str">
-        <x:v>https://bmvc2026.bmva.org/</x:v>
+        <x:v>https://www.bmva.org/bmvc</x:v>
       </x:c>
       <x:c r="H90" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/296/</x:v>
@@ -3685,7 +3685,7 @@
         <x:v>Paper-based / two independent submission rounds</x:v>
       </x:c>
       <x:c r="G98" t="str">
-        <x:v>https://wacv.thecvf.com/Conferences/2027</x:v>
+        <x:v>https://wacv.thecvf.com/</x:v>
       </x:c>
       <x:c r="H98" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/763/</x:v>
@@ -4209,7 +4209,7 @@
         <x:v>Paper-based</x:v>
       </x:c>
       <x:c r="G112" t="str">
-        <x:v>https://2027.ieee-icra.org/</x:v>
+        <x:v>https://www.ieee-ras.org/conferences-workshops/fully-sponsored/icra</x:v>
       </x:c>
       <x:c r="H112" t="str">
         <x:v>https://portal.core.edu.au/conf-ranks/2051/</x:v>
@@ -4671,7 +4671,7 @@
         <x:v>Abstract-based</x:v>
       </x:c>
       <x:c r="G128" t="str">
-        <x:v>https://fisica.ufpr.br/DDaysLAC2026/index.html</x:v>
+        <x:v>https://dynamicsdays.info/lac</x:v>
       </x:c>
       <x:c r="H128"/>
       <x:c r="I128"/>

--- a/data/core_conferences_normalized_tags.xlsx
+++ b/data/core_conferences_normalized_tags.xlsx
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CoreConferencesTable" displayName="CoreConferencesTable" ref="A1:N130" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CoreConferencesTable" displayName="CoreConferencesTable" ref="A1:N131" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Conference"/>
     <x:tableColumn id="2" name="TAGS"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ConferenceScope" displayName="ConferenceScope" ref="A1:F80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ConferenceScope" displayName="ConferenceScope" ref="A1:F81" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Series"/>
     <x:tableColumn id="2" name="Additional topics"/>
@@ -4737,6 +4737,34 @@
       <x:c r="M130"/>
       <x:c r="N130"/>
     </x:row>
+    <x:row r="131" ht="15" hidden="0" customHeight="1">
+      <x:c r="A131" t="str">
+        <x:v>AIiH</x:v>
+      </x:c>
+      <x:c r="B131" s="12" t="str">
+        <x:v>Healthcare &amp; Clinical AI; Biomedical Imaging; Machine Learning; Signal Processing</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>M</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E131"/>
+      <x:c r="F131" s="12" t="str">
+        <x:v>Full papers (double-blind, proceedings) or abstracts (posters/spotlights, Zenodo); late-breaking abstracts and STARS surveys</x:v>
+      </x:c>
+      <x:c r="G131" t="str">
+        <x:v>https://aiih.cc/</x:v>
+      </x:c>
+      <x:c r="H131"/>
+      <x:c r="I131"/>
+      <x:c r="J131"/>
+      <x:c r="K131" s="16"/>
+      <x:c r="L131" s="17"/>
+      <x:c r="M131"/>
+      <x:c r="N131"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
@@ -6713,6 +6741,26 @@
         <x:v>46302</x:v>
       </x:c>
     </x:row>
+    <x:row r="81" ht="60" hidden="0" customHeight="1">
+      <x:c r="A81" s="20" t="str">
+        <x:v>AIiH</x:v>
+      </x:c>
+      <x:c r="B81" s="20" t="str">
+        <x:v>Ethics &amp; Governance; Privacy-preserving ML; Human-AI Interaction &amp; Deployment</x:v>
+      </x:c>
+      <x:c r="C81" s="20" t="str">
+        <x:v>Artificial intelligence for healthcare and medicine, including predictive analytics, early diagnosis and prevention, machine and deep learning on health data, AI-aided medical signal processing and imaging, digital pathology and neurology, drug discovery, digital twins and precision medicine. Ethics, patient data privacy and patient-centred deployment are recurring themes. Original research papers, abstracts and state-of-the-art surveys are accepted.</x:v>
+      </x:c>
+      <x:c r="D81" s="21" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E81" s="20" t="str">
+        <x:v>https://aiih.cc/call-for-papers/; https://aiih.cc/call-for-stars/</x:v>
+      </x:c>
+      <x:c r="F81" s="22" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">

--- a/data/core_conferences_normalized_tags.xlsx
+++ b/data/core_conferences_normalized_tags.xlsx
@@ -920,7 +920,7 @@
         <x:v>TS4H</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>Time Series &amp; Sequential Data; Healthcare &amp; Clinical AI; Signal Processing; Explainability &amp; Interpretability</x:v>
+        <x:v>Healthcare &amp; Clinical AI; Time Series &amp; Sequential Data; Signal Processing; Deep Representation Learning</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
         <x:v>S</x:v>
@@ -930,10 +930,10 @@
       </x:c>
       <x:c r="E16" s="14"/>
       <x:c r="F16" s="14" t="str">
-        <x:v>Workshop / paper-based</x:v>
+        <x:v>Workshop / non-archival short paper</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>https://timeseries4health.github.io/</x:v>
+        <x:v>https://structureddata4health.github.io/</x:v>
       </x:c>
       <x:c r="H16"/>
       <x:c r="I16"/>
